--- a/results/Int Task Remove ACC -0.0/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_6_permute.xlsx
@@ -440,177 +440,177 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7610282354823228</v>
+        <v>0.778239648322935</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7715065589505679</v>
+        <v>0.7825481256332321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7645118447715031</v>
+        <v>0.7808150695888658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7589693982296166</v>
+        <v>0.7768257078867381</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7516355716418706</v>
+        <v>0.7656258332000214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7568905641763984</v>
+        <v>0.7698076641070762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7567880805737748</v>
+        <v>0.7674288780461793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7472937663307204</v>
+        <v>0.7554291313389858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7321920159441155</v>
+        <v>0.7529353636751452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7412638977763558</v>
+        <v>0.7301765050925185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7398382925398603</v>
+        <v>0.7322095131445635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7397999653388792</v>
+        <v>0.7406165013597825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7437509998400256</v>
+        <v>0.7826581080360475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7354648256278995</v>
+        <v>0.7813091572015145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7357206180344478</v>
+        <v>0.7874848357596118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7357206180344478</v>
+        <v>0.7809700447928332</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7372495400735882</v>
+        <v>0.7265579173998826</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7372303764730976</v>
+        <v>0.7248190289553671</v>
       </c>
     </row>
     <row r="20">
@@ -620,707 +620,707 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7407714765637499</v>
+        <v>0.6824033154695248</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7456165346877832</v>
+        <v>0.6861177211646137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7261096557884072</v>
+        <v>0.6861177211646137</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7240958113368527</v>
+        <v>0.6893530368474377</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7231559617127926</v>
+        <v>0.6933882245507386</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7327269303578094</v>
+        <v>0.6790280221831173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7093265077587586</v>
+        <v>0.6997130459126539</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7221144616861302</v>
+        <v>0.7000263291206741</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7221144616861302</v>
+        <v>0.7115994774169466</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7337634311843438</v>
+        <v>0.7138499506745588</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7358039380365808</v>
+        <v>0.711037067402549</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7366279728576761</v>
+        <v>0.6869284247853678</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.732574454753906</v>
+        <v>0.6869284247853678</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.732574454753906</v>
+        <v>0.6869284247853678</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7403282141524024</v>
+        <v>0.6968568362395351</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7179068015784141</v>
+        <v>0.6686571815176239</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7200614568335733</v>
+        <v>0.665351877033008</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7108737601983683</v>
+        <v>0.6716617007945396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.704998866847971</v>
+        <v>0.6652752226310457</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7043723004319309</v>
+        <v>0.6404633591958619</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7058870580707087</v>
+        <v>0.6100448928171492</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7058870580707087</v>
+        <v>0.5996048965498854</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7049655388471178</v>
+        <v>0.5914153735402335</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7079833893243748</v>
+        <v>0.5880334146536554</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7143315402868875</v>
+        <v>0.5907504799232123</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7035715952114329</v>
+        <v>0.5964404028688743</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7144215258891911</v>
+        <v>0.5764427691569349</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6891647336426172</v>
+        <v>0.5750746547219112</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6919717845144777</v>
+        <v>0.5778683743934304</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6770108449314776</v>
+        <v>0.5757970391404041</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6761734789100411</v>
+        <v>0.5777917199914679</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6720224764037754</v>
+        <v>0.56690429531275</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6668141430704421</v>
+        <v>0.5662777288967099</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6655610102383619</v>
+        <v>0.5661177544926146</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.684658787927265</v>
+        <v>0.565510351677065</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6804003026182477</v>
+        <v>0.5359859089212393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6646661534154535</v>
+        <v>0.5350202300965179</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.67887304697915</v>
+        <v>0.5413425518583693</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6833623286940755</v>
+        <v>0.5355309817095931</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.694806330987042</v>
+        <v>0.5445070455393803</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7014619327574254</v>
+        <v>0.5351527088999093</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6956062030075187</v>
+        <v>0.5491596344584867</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6956062030075187</v>
+        <v>0.5517425545246094</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6742662840612168</v>
+        <v>0.5517425545246094</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6414315376206474</v>
+        <v>0.5193110768943636</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6538203887378019</v>
+        <v>0.5041260065056258</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6532196515224231</v>
+        <v>0.5077904201994348</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5915520183437317</v>
+        <v>0.4604379965872127</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6198924838692476</v>
+        <v>0.4623368594358236</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6198924838692476</v>
+        <v>0.472022809683784</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6014354369967472</v>
+        <v>0.4745740681490961</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6099065816136084</v>
+        <v>0.4773169626193143</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5444437223377593</v>
+        <v>0.4052543259745107</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5241644670186103</v>
+        <v>0.4192579187330027</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.520347577720898</v>
+        <v>0.4134971737855276</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.521562383351997</v>
+        <v>0.4105943049112142</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5151184143870314</v>
+        <v>0.4006209006558951</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5481198008318668</v>
+        <v>0.4006209006558951</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5071396909827761</v>
+        <v>0.4958873246947155</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5316391044099611</v>
+        <v>0.485503986028902</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5336337852610249</v>
+        <v>0.5028562096731189</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5010673292273236</v>
+        <v>0.5058099037487336</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4886318189089746</v>
+        <v>0.5089177398282941</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4886318189089746</v>
+        <v>0.5083486642137258</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4958948234949075</v>
+        <v>0.5083486642137258</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4924553738068576</v>
+        <v>0.5113465178904708</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.49689882952061</v>
+        <v>0.512695468725004</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5246577214312377</v>
+        <v>0.5160715952114329</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5146784847757692</v>
+        <v>0.5258850250626567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5016813976430438</v>
+        <v>0.5309100543912973</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5003324468085106</v>
+        <v>0.5003899376099824</v>
       </c>
     </row>
   </sheetData>
